--- a/ConvertData/EXCEL_MARK_STEEL/MarkSteel.xlsx
+++ b/ConvertData/EXCEL_MARK_STEEL/MarkSteel.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disk\YandexDisk\001. Программирование\ForWorking\ConvertData\ConvertData\EXCEL_MARK_STEEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disk\YandexDisk\Programmings\ForWorking\ConvertData\ConvertData\EXCEL_MARK_STEEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2076B8-E3EC-4378-93BD-D4B29DF34FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{764D00E2-6049-4EE3-A148-CEA6CE0A52A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Steel" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Steel!$A$1:$I$121</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -25,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="39">
-  <si>
-    <t>Steel</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="40">
   <si>
     <t>tmin</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>Ru</t>
-  </si>
-  <si>
-    <t>if</t>
   </si>
   <si>
     <t>C235</t>
@@ -142,6 +139,15 @@
   </si>
   <si>
     <t>Table_B.5</t>
+  </si>
+  <si>
+    <t>caseParametr_t</t>
+  </si>
+  <si>
+    <t>of</t>
+  </si>
+  <si>
+    <t>Steel</t>
   </si>
 </sst>
 </file>
@@ -527,46 +533,47 @@
   <dimension ref="A1:I121"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" customWidth="1"/>
+    <col min="3" max="8" width="9.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1">
         <v>2</v>
@@ -587,15 +594,15 @@
         <v>350</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -616,15 +623,15 @@
         <v>360</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -644,16 +651,16 @@
       <c r="H4" s="1">
         <v>370</v>
       </c>
-      <c r="I4" s="1">
-        <v>0</v>
+      <c r="I4" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -673,16 +680,16 @@
       <c r="H5" s="1">
         <v>370</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
+      <c r="I5" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -702,16 +709,16 @@
       <c r="H6" s="1">
         <v>360</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
+      <c r="I6" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1">
         <v>20</v>
@@ -731,16 +738,16 @@
       <c r="H7" s="1">
         <v>360</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
+      <c r="I7" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -761,15 +768,15 @@
         <v>460</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
@@ -790,15 +797,15 @@
         <v>480</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1">
         <v>16</v>
@@ -818,16 +825,16 @@
       <c r="H10" s="1">
         <v>480</v>
       </c>
-      <c r="I10" s="1">
-        <v>0</v>
+      <c r="I10" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
         <v>40</v>
@@ -847,16 +854,16 @@
       <c r="H11" s="1">
         <v>480</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
+      <c r="I11" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1">
         <v>60</v>
@@ -876,16 +883,16 @@
       <c r="H12" s="1">
         <v>480</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
+      <c r="I12" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1">
         <v>80</v>
@@ -905,16 +912,16 @@
       <c r="H13" s="1">
         <v>460</v>
       </c>
-      <c r="I13" s="1">
-        <v>0</v>
+      <c r="I13" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -926,7 +933,7 @@
         <v>295</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="G14" s="1">
         <v>285</v>
@@ -934,16 +941,16 @@
       <c r="H14" s="1">
         <v>460</v>
       </c>
-      <c r="I14" s="1">
-        <v>0</v>
+      <c r="I14" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
         <v>160</v>
@@ -963,16 +970,16 @@
       <c r="H15" s="1">
         <v>460</v>
       </c>
-      <c r="I15" s="1">
-        <v>0</v>
+      <c r="I15" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" s="1">
         <v>200</v>
@@ -992,16 +999,16 @@
       <c r="H16" s="1">
         <v>440</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
+      <c r="I16" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="1">
         <v>260</v>
@@ -1021,16 +1028,16 @@
       <c r="H17" s="1">
         <v>440</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
+      <c r="I17" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -1050,16 +1057,16 @@
       <c r="H18" s="1">
         <v>430</v>
       </c>
-      <c r="I18" s="1">
-        <v>0</v>
+      <c r="I18" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1">
         <v>2</v>
@@ -1080,15 +1087,15 @@
         <v>480</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1">
         <v>16</v>
@@ -1108,16 +1115,16 @@
       <c r="H20" s="1">
         <v>480</v>
       </c>
-      <c r="I20" s="1">
-        <v>0</v>
+      <c r="I20" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1137,16 +1144,16 @@
       <c r="H21" s="1">
         <v>480</v>
       </c>
-      <c r="I21" s="1">
-        <v>0</v>
+      <c r="I21" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
@@ -1167,15 +1174,15 @@
         <v>480</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" s="1">
         <v>16</v>
@@ -1195,16 +1202,16 @@
       <c r="H23" s="1">
         <v>480</v>
       </c>
-      <c r="I23" s="1">
-        <v>0</v>
+      <c r="I23" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C24" s="1">
         <v>5</v>
@@ -1225,15 +1232,15 @@
         <v>505</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C25" s="1">
         <v>16</v>
@@ -1253,16 +1260,16 @@
       <c r="H25" s="1">
         <v>505</v>
       </c>
-      <c r="I25" s="1">
-        <v>0</v>
+      <c r="I25" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C26" s="1">
         <v>40</v>
@@ -1282,16 +1289,16 @@
       <c r="H26" s="1">
         <v>505</v>
       </c>
-      <c r="I26" s="1">
-        <v>0</v>
+      <c r="I26" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C27" s="1">
         <v>60</v>
@@ -1311,16 +1318,16 @@
       <c r="H27" s="1">
         <v>500</v>
       </c>
-      <c r="I27" s="1">
-        <v>0</v>
+      <c r="I27" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="1">
         <v>80</v>
@@ -1340,16 +1347,16 @@
       <c r="H28" s="1">
         <v>500</v>
       </c>
-      <c r="I28" s="1">
-        <v>0</v>
+      <c r="I28" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C29" s="1">
         <v>100</v>
@@ -1369,16 +1376,16 @@
       <c r="H29" s="1">
         <v>500</v>
       </c>
-      <c r="I29" s="1">
-        <v>0</v>
+      <c r="I29" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
@@ -1399,15 +1406,15 @@
         <v>505</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C31" s="1">
         <v>5</v>
@@ -1428,15 +1435,15 @@
         <v>525</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32" s="1">
         <v>16</v>
@@ -1456,16 +1463,16 @@
       <c r="H32" s="1">
         <v>525</v>
       </c>
-      <c r="I32" s="1">
-        <v>0</v>
+      <c r="I32" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C33" s="1">
         <v>40</v>
@@ -1485,16 +1492,16 @@
       <c r="H33" s="1">
         <v>525</v>
       </c>
-      <c r="I33" s="1">
-        <v>0</v>
+      <c r="I33" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C34" s="1">
         <v>60</v>
@@ -1514,16 +1521,16 @@
       <c r="H34" s="1">
         <v>520</v>
       </c>
-      <c r="I34" s="1">
-        <v>0</v>
+      <c r="I34" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C35" s="1">
         <v>80</v>
@@ -1543,16 +1550,16 @@
       <c r="H35" s="1">
         <v>520</v>
       </c>
-      <c r="I35" s="1">
-        <v>0</v>
+      <c r="I35" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C36" s="1">
         <v>100</v>
@@ -1572,16 +1579,16 @@
       <c r="H36" s="1">
         <v>520</v>
       </c>
-      <c r="I36" s="1">
-        <v>0</v>
+      <c r="I36" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -1602,15 +1609,15 @@
         <v>625</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="C38" s="1">
         <v>8</v>
@@ -1631,15 +1638,15 @@
         <v>670</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C39" s="1">
         <v>8</v>
@@ -1654,21 +1661,21 @@
         <v>785</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
+        <v>690</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C40" s="1">
         <v>0</v>
@@ -1689,15 +1696,15 @@
         <v>370</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C41" s="1">
         <v>11</v>
@@ -1718,15 +1725,15 @@
         <v>360</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C42" s="1">
         <v>20</v>
@@ -1746,16 +1753,16 @@
       <c r="H42" s="1">
         <v>360</v>
       </c>
-      <c r="I42" s="1">
-        <v>0</v>
+      <c r="I42" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C43" s="1">
         <v>40</v>
@@ -1775,16 +1782,16 @@
       <c r="H43" s="1">
         <v>360</v>
       </c>
-      <c r="I43" s="1">
-        <v>0</v>
+      <c r="I43" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C44" s="1">
         <v>60</v>
@@ -1804,16 +1811,16 @@
       <c r="H44" s="1">
         <v>360</v>
       </c>
-      <c r="I44" s="1">
-        <v>0</v>
+      <c r="I44" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C45" s="1">
         <v>80</v>
@@ -1833,16 +1840,16 @@
       <c r="H45" s="1">
         <v>360</v>
       </c>
-      <c r="I45" s="1">
-        <v>0</v>
+      <c r="I45" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1">
         <v>101</v>
@@ -1862,16 +1869,16 @@
       <c r="H46" s="1">
         <v>350</v>
       </c>
-      <c r="I46" s="1">
-        <v>0</v>
+      <c r="I46" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C47" s="1">
         <v>0</v>
@@ -1892,15 +1899,15 @@
         <v>370</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C48" s="1">
         <v>11</v>
@@ -1921,15 +1928,15 @@
         <v>360</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C49" s="1">
         <v>20</v>
@@ -1949,16 +1956,16 @@
       <c r="H49" s="1">
         <v>360</v>
       </c>
-      <c r="I49" s="1">
-        <v>0</v>
+      <c r="I49" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C50" s="1">
         <v>40</v>
@@ -1978,16 +1985,16 @@
       <c r="H50" s="1">
         <v>360</v>
       </c>
-      <c r="I50" s="1">
-        <v>0</v>
+      <c r="I50" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1">
         <v>60</v>
@@ -2007,16 +2014,16 @@
       <c r="H51" s="1">
         <v>360</v>
       </c>
-      <c r="I51" s="1">
-        <v>0</v>
+      <c r="I51" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C52" s="1">
         <v>80</v>
@@ -2036,16 +2043,16 @@
       <c r="H52" s="1">
         <v>360</v>
       </c>
-      <c r="I52" s="1">
-        <v>0</v>
+      <c r="I52" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C53" s="1">
         <v>101</v>
@@ -2065,16 +2072,16 @@
       <c r="H53" s="1">
         <v>350</v>
       </c>
-      <c r="I53" s="1">
-        <v>0</v>
+      <c r="I53" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C54" s="1">
         <v>0</v>
@@ -2095,15 +2102,15 @@
         <v>470</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C55" s="1">
         <v>11</v>
@@ -2124,15 +2131,15 @@
         <v>460</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C56" s="1">
         <v>20</v>
@@ -2152,16 +2159,16 @@
       <c r="H56" s="1">
         <v>450</v>
       </c>
-      <c r="I56" s="1">
-        <v>0</v>
+      <c r="I56" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C57" s="1">
         <v>40</v>
@@ -2181,16 +2188,16 @@
       <c r="H57" s="1">
         <v>440</v>
       </c>
-      <c r="I57" s="1">
-        <v>0</v>
+      <c r="I57" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C58" s="1">
         <v>0</v>
@@ -2211,15 +2218,15 @@
         <v>480</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C59" s="1">
         <v>11</v>
@@ -2240,15 +2247,15 @@
         <v>460</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C60" s="1">
         <v>20</v>
@@ -2268,16 +2275,16 @@
       <c r="H60" s="1">
         <v>450</v>
       </c>
-      <c r="I60" s="1">
-        <v>0</v>
+      <c r="I60" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C61" s="1">
         <v>40</v>
@@ -2297,16 +2304,16 @@
       <c r="H61" s="1">
         <v>440</v>
       </c>
-      <c r="I61" s="1">
-        <v>0</v>
+      <c r="I61" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C62" s="1">
         <v>0</v>
@@ -2327,15 +2334,15 @@
         <v>460</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C63" s="1">
         <v>21</v>
@@ -2356,15 +2363,15 @@
         <v>460</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C64" s="1">
         <v>40</v>
@@ -2384,16 +2391,16 @@
       <c r="H64" s="1">
         <v>460</v>
       </c>
-      <c r="I64" s="1">
-        <v>0</v>
+      <c r="I64" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C65" s="1">
         <v>60</v>
@@ -2413,16 +2420,16 @@
       <c r="H65" s="1">
         <v>450</v>
       </c>
-      <c r="I65" s="1">
-        <v>0</v>
+      <c r="I65" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C66" s="1">
         <v>80</v>
@@ -2442,16 +2449,16 @@
       <c r="H66" s="1">
         <v>450</v>
       </c>
-      <c r="I66" s="1">
-        <v>0</v>
+      <c r="I66" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C67" s="1">
         <v>101</v>
@@ -2471,16 +2478,16 @@
       <c r="H67" s="1">
         <v>450</v>
       </c>
-      <c r="I67" s="1">
-        <v>0</v>
+      <c r="I67" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C68" s="1">
         <v>0</v>
@@ -2501,15 +2508,15 @@
         <v>460</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C69" s="1">
         <v>21</v>
@@ -2529,16 +2536,16 @@
       <c r="H69" s="1">
         <v>460</v>
       </c>
-      <c r="I69" s="1">
-        <v>0</v>
+      <c r="I69" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C70" s="1">
         <v>40</v>
@@ -2558,16 +2565,16 @@
       <c r="H70" s="1">
         <v>460</v>
       </c>
-      <c r="I70" s="1">
-        <v>0</v>
+      <c r="I70" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C71" s="1">
         <v>0</v>
@@ -2588,15 +2595,15 @@
         <v>505</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C72" s="1">
         <v>31</v>
@@ -2617,15 +2624,15 @@
         <v>480</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C73" s="1">
         <v>60</v>
@@ -2645,16 +2652,16 @@
       <c r="H73" s="1">
         <v>470</v>
       </c>
-      <c r="I73" s="1">
-        <v>0</v>
+      <c r="I73" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C74" s="1">
         <v>80</v>
@@ -2674,16 +2681,16 @@
       <c r="H74" s="1">
         <v>470</v>
       </c>
-      <c r="I74" s="1">
-        <v>0</v>
+      <c r="I74" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C75" s="1">
         <v>101</v>
@@ -2703,16 +2710,16 @@
       <c r="H75" s="1">
         <v>460</v>
       </c>
-      <c r="I75" s="1">
-        <v>0</v>
+      <c r="I75" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C76" s="1">
         <v>0</v>
@@ -2733,15 +2740,15 @@
         <v>585</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C77" s="1">
         <v>21</v>
@@ -2762,15 +2769,15 @@
         <v>545</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C78" s="1">
         <v>30</v>
@@ -2790,16 +2797,16 @@
       <c r="H78" s="1">
         <v>505</v>
       </c>
-      <c r="I78" s="1">
-        <v>0</v>
+      <c r="I78" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C79" s="1">
         <v>80</v>
@@ -2819,16 +2826,16 @@
       <c r="H79" s="1">
         <v>505</v>
       </c>
-      <c r="I79" s="1">
-        <v>0</v>
+      <c r="I79" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C80" s="1">
         <v>101</v>
@@ -2848,16 +2855,16 @@
       <c r="H80" s="1">
         <v>490</v>
       </c>
-      <c r="I80" s="1">
-        <v>0</v>
+      <c r="I80" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C81" s="1">
         <v>4</v>
@@ -2878,15 +2885,15 @@
         <v>360</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C82" s="1">
         <v>20</v>
@@ -2906,16 +2913,16 @@
       <c r="H82" s="1">
         <v>360</v>
       </c>
-      <c r="I82" s="1">
-        <v>0</v>
+      <c r="I82" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C83" s="1">
         <v>4</v>
@@ -2936,15 +2943,15 @@
         <v>370</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
         <v>10</v>
@@ -2964,16 +2971,16 @@
       <c r="H84" s="1">
         <v>360</v>
       </c>
-      <c r="I84" s="1">
-        <v>0</v>
+      <c r="I84" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C85" s="1">
         <v>20</v>
@@ -2993,16 +3000,16 @@
       <c r="H85" s="1">
         <v>360</v>
       </c>
-      <c r="I85" s="1">
-        <v>0</v>
+      <c r="I85" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C86" s="1">
         <v>4</v>
@@ -3023,15 +3030,15 @@
         <v>470</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C87" s="1">
         <v>10</v>
@@ -3051,16 +3058,16 @@
       <c r="H87" s="1">
         <v>460</v>
       </c>
-      <c r="I87" s="1">
-        <v>0</v>
+      <c r="I87" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C88" s="1">
         <v>20</v>
@@ -3080,16 +3087,16 @@
       <c r="H88" s="1">
         <v>450</v>
       </c>
-      <c r="I88" s="1">
-        <v>0</v>
+      <c r="I88" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C89" s="1">
         <v>4</v>
@@ -3110,15 +3117,15 @@
         <v>470</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C90" s="1">
         <v>5</v>
@@ -3139,15 +3146,15 @@
         <v>480</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C91" s="1">
         <v>16</v>
@@ -3167,16 +3174,16 @@
       <c r="H91" s="1">
         <v>470</v>
       </c>
-      <c r="I91" s="1">
-        <v>0</v>
+      <c r="I91" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C92" s="1">
         <v>40</v>
@@ -3196,16 +3203,16 @@
       <c r="H92" s="1">
         <v>460</v>
       </c>
-      <c r="I92" s="1">
-        <v>0</v>
+      <c r="I92" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C93" s="1">
         <v>5</v>
@@ -3226,15 +3233,15 @@
         <v>480</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C94" s="1">
         <v>16</v>
@@ -3254,16 +3261,16 @@
       <c r="H94" s="1">
         <v>470</v>
       </c>
-      <c r="I94" s="1">
-        <v>0</v>
+      <c r="I94" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C95" s="1">
         <v>40</v>
@@ -3283,16 +3290,16 @@
       <c r="H95" s="1">
         <v>460</v>
       </c>
-      <c r="I95" s="1">
-        <v>0</v>
+      <c r="I95" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C96" s="1">
         <v>5</v>
@@ -3313,15 +3320,15 @@
         <v>505</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C97" s="1">
         <v>10</v>
@@ -3341,16 +3348,16 @@
       <c r="H97" s="1">
         <v>480</v>
       </c>
-      <c r="I97" s="1">
-        <v>0</v>
+      <c r="I97" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C98" s="1">
         <v>20</v>
@@ -3370,16 +3377,16 @@
       <c r="H98" s="1">
         <v>480</v>
       </c>
-      <c r="I98" s="1">
-        <v>0</v>
+      <c r="I98" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C99" s="1">
         <v>40</v>
@@ -3399,16 +3406,16 @@
       <c r="H99" s="1">
         <v>475</v>
       </c>
-      <c r="I99" s="1">
-        <v>0</v>
+      <c r="I99" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C100" s="1">
         <v>5</v>
@@ -3429,15 +3436,15 @@
         <v>585</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C101" s="1">
         <v>10</v>
@@ -3457,16 +3464,16 @@
       <c r="H101" s="1">
         <v>565</v>
       </c>
-      <c r="I101" s="1">
-        <v>0</v>
+      <c r="I101" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C102" s="1">
         <v>20</v>
@@ -3486,16 +3493,16 @@
       <c r="H102" s="1">
         <v>535</v>
       </c>
-      <c r="I102" s="1">
-        <v>0</v>
+      <c r="I102" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C103" s="1">
         <v>40</v>
@@ -3515,16 +3522,16 @@
       <c r="H103" s="1">
         <v>505</v>
       </c>
-      <c r="I103" s="1">
-        <v>0</v>
+      <c r="I103" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C104" s="1">
         <v>21</v>
@@ -3545,15 +3552,15 @@
         <v>460</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C105" s="1">
         <v>40</v>
@@ -3573,16 +3580,16 @@
       <c r="H105" s="1">
         <v>460</v>
       </c>
-      <c r="I105" s="1">
-        <v>0</v>
+      <c r="I105" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C106" s="1">
         <v>60</v>
@@ -3602,16 +3609,16 @@
       <c r="H106" s="1">
         <v>450</v>
       </c>
-      <c r="I106" s="1">
-        <v>0</v>
+      <c r="I106" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C107" s="1">
         <v>80</v>
@@ -3631,16 +3638,16 @@
       <c r="H107" s="1">
         <v>450</v>
       </c>
-      <c r="I107" s="1">
-        <v>0</v>
+      <c r="I107" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C108" s="1">
         <v>101</v>
@@ -3660,16 +3667,16 @@
       <c r="H108" s="1">
         <v>450</v>
       </c>
-      <c r="I108" s="1">
-        <v>0</v>
+      <c r="I108" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
@@ -3690,15 +3697,15 @@
         <v>460</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C110" s="1">
         <v>21</v>
@@ -3718,16 +3725,16 @@
       <c r="H110" s="1">
         <v>460</v>
       </c>
-      <c r="I110" s="1">
-        <v>0</v>
+      <c r="I110" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C111" s="1">
         <v>40</v>
@@ -3747,16 +3754,16 @@
       <c r="H111" s="1">
         <v>460</v>
       </c>
-      <c r="I111" s="1">
-        <v>0</v>
+      <c r="I111" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C112" s="1">
         <v>0</v>
@@ -3777,15 +3784,15 @@
         <v>505</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C113" s="1">
         <v>31</v>
@@ -3806,15 +3813,15 @@
         <v>480</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C114" s="1">
         <v>60</v>
@@ -3834,16 +3841,16 @@
       <c r="H114" s="1">
         <v>470</v>
       </c>
-      <c r="I114" s="1">
-        <v>0</v>
+      <c r="I114" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C115" s="1">
         <v>80</v>
@@ -3863,16 +3870,16 @@
       <c r="H115" s="1">
         <v>470</v>
       </c>
-      <c r="I115" s="1">
-        <v>0</v>
+      <c r="I115" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C116" s="1">
         <v>101</v>
@@ -3892,16 +3899,16 @@
       <c r="H116" s="1">
         <v>460</v>
       </c>
-      <c r="I116" s="1">
-        <v>0</v>
+      <c r="I116" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="1">
         <v>0</v>
@@ -3922,15 +3929,15 @@
         <v>585</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C118" s="1">
         <v>21</v>
@@ -3951,15 +3958,15 @@
         <v>545</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C119" s="1">
         <v>30</v>
@@ -3979,16 +3986,16 @@
       <c r="H119" s="1">
         <v>505</v>
       </c>
-      <c r="I119" s="1">
-        <v>0</v>
+      <c r="I119" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C120" s="1">
         <v>80</v>
@@ -4008,16 +4015,16 @@
       <c r="H120" s="1">
         <v>505</v>
       </c>
-      <c r="I120" s="1">
-        <v>0</v>
+      <c r="I120" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C121" s="1">
         <v>101</v>
@@ -4037,8 +4044,8 @@
       <c r="H121" s="1">
         <v>490</v>
       </c>
-      <c r="I121" s="1">
-        <v>0</v>
+      <c r="I121" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/ConvertData/EXCEL_MARK_STEEL/MarkSteel.xlsx
+++ b/ConvertData/EXCEL_MARK_STEEL/MarkSteel.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disk\YandexDisk\001. Программирование\ForWorking\ConvertData\ConvertData\EXCEL_MARK_STEEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2076B8-E3EC-4378-93BD-D4B29DF34FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E685E0F4-A3BE-4AE9-87DE-E0F95B9A16AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Steel" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Steel!$A$1:$I$121</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -25,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="39">
-  <si>
-    <t>Steel</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="40">
   <si>
     <t>tmin</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>Ru</t>
-  </si>
-  <si>
-    <t>if</t>
   </si>
   <si>
     <t>C235</t>
@@ -142,6 +139,15 @@
   </si>
   <si>
     <t>Table_B.5</t>
+  </si>
+  <si>
+    <t>caseParametr_t</t>
+  </si>
+  <si>
+    <t>of</t>
+  </si>
+  <si>
+    <t>Steel</t>
   </si>
 </sst>
 </file>
@@ -527,46 +533,47 @@
   <dimension ref="A1:I121"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="1" customWidth="1"/>
+    <col min="3" max="8" width="9.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1">
         <v>2</v>
@@ -587,15 +594,15 @@
         <v>350</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -616,15 +623,15 @@
         <v>360</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -644,16 +651,16 @@
       <c r="H4" s="1">
         <v>370</v>
       </c>
-      <c r="I4" s="1">
-        <v>0</v>
+      <c r="I4" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
@@ -673,16 +680,16 @@
       <c r="H5" s="1">
         <v>370</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
+      <c r="I5" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1">
         <v>10</v>
@@ -702,16 +709,16 @@
       <c r="H6" s="1">
         <v>360</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
+      <c r="I6" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1">
         <v>20</v>
@@ -731,16 +738,16 @@
       <c r="H7" s="1">
         <v>360</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
+      <c r="I7" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
@@ -761,15 +768,15 @@
         <v>460</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
@@ -790,15 +797,15 @@
         <v>480</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1">
         <v>16</v>
@@ -818,16 +825,16 @@
       <c r="H10" s="1">
         <v>480</v>
       </c>
-      <c r="I10" s="1">
-        <v>0</v>
+      <c r="I10" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
         <v>40</v>
@@ -847,16 +854,16 @@
       <c r="H11" s="1">
         <v>480</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
+      <c r="I11" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1">
         <v>60</v>
@@ -876,16 +883,16 @@
       <c r="H12" s="1">
         <v>480</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
+      <c r="I12" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1">
         <v>80</v>
@@ -905,16 +912,16 @@
       <c r="H13" s="1">
         <v>460</v>
       </c>
-      <c r="I13" s="1">
-        <v>0</v>
+      <c r="I13" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -926,7 +933,7 @@
         <v>295</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="G14" s="1">
         <v>285</v>
@@ -934,16 +941,16 @@
       <c r="H14" s="1">
         <v>460</v>
       </c>
-      <c r="I14" s="1">
-        <v>0</v>
+      <c r="I14" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
         <v>160</v>
@@ -963,16 +970,16 @@
       <c r="H15" s="1">
         <v>460</v>
       </c>
-      <c r="I15" s="1">
-        <v>0</v>
+      <c r="I15" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" s="1">
         <v>200</v>
@@ -992,16 +999,16 @@
       <c r="H16" s="1">
         <v>440</v>
       </c>
-      <c r="I16" s="1">
-        <v>0</v>
+      <c r="I16" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="1">
         <v>260</v>
@@ -1021,16 +1028,16 @@
       <c r="H17" s="1">
         <v>440</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
+      <c r="I17" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -1050,16 +1057,16 @@
       <c r="H18" s="1">
         <v>430</v>
       </c>
-      <c r="I18" s="1">
-        <v>0</v>
+      <c r="I18" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1">
         <v>2</v>
@@ -1080,15 +1087,15 @@
         <v>480</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1">
         <v>16</v>
@@ -1108,16 +1115,16 @@
       <c r="H20" s="1">
         <v>480</v>
       </c>
-      <c r="I20" s="1">
-        <v>0</v>
+      <c r="I20" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1137,16 +1144,16 @@
       <c r="H21" s="1">
         <v>480</v>
       </c>
-      <c r="I21" s="1">
-        <v>0</v>
+      <c r="I21" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
@@ -1167,15 +1174,15 @@
         <v>480</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" s="1">
         <v>16</v>
@@ -1195,16 +1202,16 @@
       <c r="H23" s="1">
         <v>480</v>
       </c>
-      <c r="I23" s="1">
-        <v>0</v>
+      <c r="I23" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C24" s="1">
         <v>5</v>
@@ -1225,15 +1232,15 @@
         <v>505</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C25" s="1">
         <v>16</v>
@@ -1253,16 +1260,16 @@
       <c r="H25" s="1">
         <v>505</v>
       </c>
-      <c r="I25" s="1">
-        <v>0</v>
+      <c r="I25" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C26" s="1">
         <v>40</v>
@@ -1282,16 +1289,16 @@
       <c r="H26" s="1">
         <v>505</v>
       </c>
-      <c r="I26" s="1">
-        <v>0</v>
+      <c r="I26" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C27" s="1">
         <v>60</v>
@@ -1311,16 +1318,16 @@
       <c r="H27" s="1">
         <v>500</v>
       </c>
-      <c r="I27" s="1">
-        <v>0</v>
+      <c r="I27" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="1">
         <v>80</v>
@@ -1340,16 +1347,16 @@
       <c r="H28" s="1">
         <v>500</v>
       </c>
-      <c r="I28" s="1">
-        <v>0</v>
+      <c r="I28" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C29" s="1">
         <v>100</v>
@@ -1369,16 +1376,16 @@
       <c r="H29" s="1">
         <v>500</v>
       </c>
-      <c r="I29" s="1">
-        <v>0</v>
+      <c r="I29" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C30" s="1">
         <v>2</v>
@@ -1399,15 +1406,15 @@
         <v>505</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C31" s="1">
         <v>5</v>
@@ -1428,15 +1435,15 @@
         <v>525</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32" s="1">
         <v>16</v>
@@ -1456,16 +1463,16 @@
       <c r="H32" s="1">
         <v>525</v>
       </c>
-      <c r="I32" s="1">
-        <v>0</v>
+      <c r="I32" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C33" s="1">
         <v>40</v>
@@ -1485,16 +1492,16 @@
       <c r="H33" s="1">
         <v>525</v>
       </c>
-      <c r="I33" s="1">
-        <v>0</v>
+      <c r="I33" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C34" s="1">
         <v>60</v>
@@ -1514,16 +1521,16 @@
       <c r="H34" s="1">
         <v>520</v>
       </c>
-      <c r="I34" s="1">
-        <v>0</v>
+      <c r="I34" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C35" s="1">
         <v>80</v>
@@ -1543,16 +1550,16 @@
       <c r="H35" s="1">
         <v>520</v>
       </c>
-      <c r="I35" s="1">
-        <v>0</v>
+      <c r="I35" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C36" s="1">
         <v>100</v>
@@ -1572,16 +1579,16 @@
       <c r="H36" s="1">
         <v>520</v>
       </c>
-      <c r="I36" s="1">
-        <v>0</v>
+      <c r="I36" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -1602,15 +1609,15 @@
         <v>625</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="C38" s="1">
         <v>8</v>
@@ -1631,15 +1638,15 @@
         <v>670</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C39" s="1">
         <v>8</v>
@@ -1654,21 +1661,21 @@
         <v>785</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
+        <v>690</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C40" s="1">
         <v>0</v>
@@ -1689,15 +1696,15 @@
         <v>370</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C41" s="1">
         <v>11</v>
@@ -1718,15 +1725,15 @@
         <v>360</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C42" s="1">
         <v>20</v>
@@ -1746,16 +1753,16 @@
       <c r="H42" s="1">
         <v>360</v>
       </c>
-      <c r="I42" s="1">
-        <v>0</v>
+      <c r="I42" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C43" s="1">
         <v>40</v>
@@ -1775,16 +1782,16 @@
       <c r="H43" s="1">
         <v>360</v>
       </c>
-      <c r="I43" s="1">
-        <v>0</v>
+      <c r="I43" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C44" s="1">
         <v>60</v>
@@ -1804,16 +1811,16 @@
       <c r="H44" s="1">
         <v>360</v>
       </c>
-      <c r="I44" s="1">
-        <v>0</v>
+      <c r="I44" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C45" s="1">
         <v>80</v>
@@ -1833,16 +1840,16 @@
       <c r="H45" s="1">
         <v>360</v>
       </c>
-      <c r="I45" s="1">
-        <v>0</v>
+      <c r="I45" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C46" s="1">
         <v>101</v>
@@ -1862,16 +1869,16 @@
       <c r="H46" s="1">
         <v>350</v>
       </c>
-      <c r="I46" s="1">
-        <v>0</v>
+      <c r="I46" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C47" s="1">
         <v>0</v>
@@ -1892,15 +1899,15 @@
         <v>370</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C48" s="1">
         <v>11</v>
@@ -1921,15 +1928,15 @@
         <v>360</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C49" s="1">
         <v>20</v>
@@ -1949,16 +1956,16 @@
       <c r="H49" s="1">
         <v>360</v>
       </c>
-      <c r="I49" s="1">
-        <v>0</v>
+      <c r="I49" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C50" s="1">
         <v>40</v>
@@ -1978,16 +1985,16 @@
       <c r="H50" s="1">
         <v>360</v>
       </c>
-      <c r="I50" s="1">
-        <v>0</v>
+      <c r="I50" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1">
         <v>60</v>
@@ -2007,16 +2014,16 @@
       <c r="H51" s="1">
         <v>360</v>
       </c>
-      <c r="I51" s="1">
-        <v>0</v>
+      <c r="I51" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C52" s="1">
         <v>80</v>
@@ -2036,16 +2043,16 @@
       <c r="H52" s="1">
         <v>360</v>
       </c>
-      <c r="I52" s="1">
-        <v>0</v>
+      <c r="I52" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C53" s="1">
         <v>101</v>
@@ -2065,16 +2072,16 @@
       <c r="H53" s="1">
         <v>350</v>
       </c>
-      <c r="I53" s="1">
-        <v>0</v>
+      <c r="I53" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C54" s="1">
         <v>0</v>
@@ -2095,15 +2102,15 @@
         <v>470</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C55" s="1">
         <v>11</v>
@@ -2124,15 +2131,15 @@
         <v>460</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C56" s="1">
         <v>20</v>
@@ -2152,16 +2159,16 @@
       <c r="H56" s="1">
         <v>450</v>
       </c>
-      <c r="I56" s="1">
-        <v>0</v>
+      <c r="I56" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C57" s="1">
         <v>40</v>
@@ -2181,16 +2188,16 @@
       <c r="H57" s="1">
         <v>440</v>
       </c>
-      <c r="I57" s="1">
-        <v>0</v>
+      <c r="I57" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C58" s="1">
         <v>0</v>
@@ -2211,15 +2218,15 @@
         <v>480</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C59" s="1">
         <v>11</v>
@@ -2240,15 +2247,15 @@
         <v>460</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C60" s="1">
         <v>20</v>
@@ -2268,16 +2275,16 @@
       <c r="H60" s="1">
         <v>450</v>
       </c>
-      <c r="I60" s="1">
-        <v>0</v>
+      <c r="I60" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C61" s="1">
         <v>40</v>
@@ -2297,16 +2304,16 @@
       <c r="H61" s="1">
         <v>440</v>
       </c>
-      <c r="I61" s="1">
-        <v>0</v>
+      <c r="I61" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C62" s="1">
         <v>0</v>
@@ -2327,15 +2334,15 @@
         <v>460</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C63" s="1">
         <v>21</v>
@@ -2356,15 +2363,15 @@
         <v>460</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C64" s="1">
         <v>40</v>
@@ -2384,16 +2391,16 @@
       <c r="H64" s="1">
         <v>460</v>
       </c>
-      <c r="I64" s="1">
-        <v>0</v>
+      <c r="I64" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C65" s="1">
         <v>60</v>
@@ -2413,16 +2420,16 @@
       <c r="H65" s="1">
         <v>450</v>
       </c>
-      <c r="I65" s="1">
-        <v>0</v>
+      <c r="I65" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C66" s="1">
         <v>80</v>
@@ -2442,16 +2449,16 @@
       <c r="H66" s="1">
         <v>450</v>
       </c>
-      <c r="I66" s="1">
-        <v>0</v>
+      <c r="I66" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C67" s="1">
         <v>101</v>
@@ -2471,16 +2478,16 @@
       <c r="H67" s="1">
         <v>450</v>
       </c>
-      <c r="I67" s="1">
-        <v>0</v>
+      <c r="I67" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C68" s="1">
         <v>0</v>
@@ -2501,15 +2508,15 @@
         <v>460</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C69" s="1">
         <v>21</v>
@@ -2529,16 +2536,16 @@
       <c r="H69" s="1">
         <v>460</v>
       </c>
-      <c r="I69" s="1">
-        <v>0</v>
+      <c r="I69" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C70" s="1">
         <v>40</v>
@@ -2558,16 +2565,16 @@
       <c r="H70" s="1">
         <v>460</v>
       </c>
-      <c r="I70" s="1">
-        <v>0</v>
+      <c r="I70" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C71" s="1">
         <v>0</v>
@@ -2588,15 +2595,15 @@
         <v>505</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C72" s="1">
         <v>31</v>
@@ -2617,15 +2624,15 @@
         <v>480</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C73" s="1">
         <v>60</v>
@@ -2645,16 +2652,16 @@
       <c r="H73" s="1">
         <v>470</v>
       </c>
-      <c r="I73" s="1">
-        <v>0</v>
+      <c r="I73" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C74" s="1">
         <v>80</v>
@@ -2674,16 +2681,16 @@
       <c r="H74" s="1">
         <v>470</v>
       </c>
-      <c r="I74" s="1">
-        <v>0</v>
+      <c r="I74" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C75" s="1">
         <v>101</v>
@@ -2703,16 +2710,16 @@
       <c r="H75" s="1">
         <v>460</v>
       </c>
-      <c r="I75" s="1">
-        <v>0</v>
+      <c r="I75" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C76" s="1">
         <v>0</v>
@@ -2733,15 +2740,15 @@
         <v>585</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C77" s="1">
         <v>21</v>
@@ -2762,15 +2769,15 @@
         <v>545</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C78" s="1">
         <v>30</v>
@@ -2790,16 +2797,16 @@
       <c r="H78" s="1">
         <v>505</v>
       </c>
-      <c r="I78" s="1">
-        <v>0</v>
+      <c r="I78" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C79" s="1">
         <v>80</v>
@@ -2819,16 +2826,16 @@
       <c r="H79" s="1">
         <v>505</v>
       </c>
-      <c r="I79" s="1">
-        <v>0</v>
+      <c r="I79" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C80" s="1">
         <v>101</v>
@@ -2848,16 +2855,16 @@
       <c r="H80" s="1">
         <v>490</v>
       </c>
-      <c r="I80" s="1">
-        <v>0</v>
+      <c r="I80" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C81" s="1">
         <v>4</v>
@@ -2878,15 +2885,15 @@
         <v>360</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C82" s="1">
         <v>20</v>
@@ -2906,16 +2913,16 @@
       <c r="H82" s="1">
         <v>360</v>
       </c>
-      <c r="I82" s="1">
-        <v>0</v>
+      <c r="I82" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C83" s="1">
         <v>4</v>
@@ -2936,15 +2943,15 @@
         <v>370</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C84" s="1">
         <v>10</v>
@@ -2964,16 +2971,16 @@
       <c r="H84" s="1">
         <v>360</v>
       </c>
-      <c r="I84" s="1">
-        <v>0</v>
+      <c r="I84" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C85" s="1">
         <v>20</v>
@@ -2993,16 +3000,16 @@
       <c r="H85" s="1">
         <v>360</v>
       </c>
-      <c r="I85" s="1">
-        <v>0</v>
+      <c r="I85" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C86" s="1">
         <v>4</v>
@@ -3023,15 +3030,15 @@
         <v>470</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C87" s="1">
         <v>10</v>
@@ -3051,16 +3058,16 @@
       <c r="H87" s="1">
         <v>460</v>
       </c>
-      <c r="I87" s="1">
-        <v>0</v>
+      <c r="I87" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C88" s="1">
         <v>20</v>
@@ -3080,16 +3087,16 @@
       <c r="H88" s="1">
         <v>450</v>
       </c>
-      <c r="I88" s="1">
-        <v>0</v>
+      <c r="I88" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C89" s="1">
         <v>4</v>
@@ -3110,15 +3117,15 @@
         <v>470</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C90" s="1">
         <v>5</v>
@@ -3139,15 +3146,15 @@
         <v>480</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C91" s="1">
         <v>16</v>
@@ -3167,16 +3174,16 @@
       <c r="H91" s="1">
         <v>470</v>
       </c>
-      <c r="I91" s="1">
-        <v>0</v>
+      <c r="I91" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C92" s="1">
         <v>40</v>
@@ -3196,16 +3203,16 @@
       <c r="H92" s="1">
         <v>460</v>
       </c>
-      <c r="I92" s="1">
-        <v>0</v>
+      <c r="I92" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C93" s="1">
         <v>5</v>
@@ -3226,15 +3233,15 @@
         <v>480</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C94" s="1">
         <v>16</v>
@@ -3254,16 +3261,16 @@
       <c r="H94" s="1">
         <v>470</v>
       </c>
-      <c r="I94" s="1">
-        <v>0</v>
+      <c r="I94" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C95" s="1">
         <v>40</v>
@@ -3283,16 +3290,16 @@
       <c r="H95" s="1">
         <v>460</v>
       </c>
-      <c r="I95" s="1">
-        <v>0</v>
+      <c r="I95" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C96" s="1">
         <v>5</v>
@@ -3313,15 +3320,15 @@
         <v>505</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C97" s="1">
         <v>10</v>
@@ -3341,16 +3348,16 @@
       <c r="H97" s="1">
         <v>480</v>
       </c>
-      <c r="I97" s="1">
-        <v>0</v>
+      <c r="I97" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C98" s="1">
         <v>20</v>
@@ -3370,16 +3377,16 @@
       <c r="H98" s="1">
         <v>480</v>
       </c>
-      <c r="I98" s="1">
-        <v>0</v>
+      <c r="I98" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C99" s="1">
         <v>40</v>
@@ -3399,16 +3406,16 @@
       <c r="H99" s="1">
         <v>475</v>
       </c>
-      <c r="I99" s="1">
-        <v>0</v>
+      <c r="I99" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C100" s="1">
         <v>5</v>
@@ -3429,15 +3436,15 @@
         <v>585</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C101" s="1">
         <v>10</v>
@@ -3457,16 +3464,16 @@
       <c r="H101" s="1">
         <v>565</v>
       </c>
-      <c r="I101" s="1">
-        <v>0</v>
+      <c r="I101" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C102" s="1">
         <v>20</v>
@@ -3486,16 +3493,16 @@
       <c r="H102" s="1">
         <v>535</v>
       </c>
-      <c r="I102" s="1">
-        <v>0</v>
+      <c r="I102" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C103" s="1">
         <v>40</v>
@@ -3515,16 +3522,16 @@
       <c r="H103" s="1">
         <v>505</v>
       </c>
-      <c r="I103" s="1">
-        <v>0</v>
+      <c r="I103" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C104" s="1">
         <v>21</v>
@@ -3545,15 +3552,15 @@
         <v>460</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C105" s="1">
         <v>40</v>
@@ -3573,16 +3580,16 @@
       <c r="H105" s="1">
         <v>460</v>
       </c>
-      <c r="I105" s="1">
-        <v>0</v>
+      <c r="I105" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C106" s="1">
         <v>60</v>
@@ -3602,16 +3609,16 @@
       <c r="H106" s="1">
         <v>450</v>
       </c>
-      <c r="I106" s="1">
-        <v>0</v>
+      <c r="I106" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C107" s="1">
         <v>80</v>
@@ -3631,16 +3638,16 @@
       <c r="H107" s="1">
         <v>450</v>
       </c>
-      <c r="I107" s="1">
-        <v>0</v>
+      <c r="I107" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C108" s="1">
         <v>101</v>
@@ -3660,16 +3667,16 @@
       <c r="H108" s="1">
         <v>450</v>
       </c>
-      <c r="I108" s="1">
-        <v>0</v>
+      <c r="I108" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
@@ -3690,15 +3697,15 @@
         <v>460</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C110" s="1">
         <v>21</v>
@@ -3718,16 +3725,16 @@
       <c r="H110" s="1">
         <v>460</v>
       </c>
-      <c r="I110" s="1">
-        <v>0</v>
+      <c r="I110" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C111" s="1">
         <v>40</v>
@@ -3747,16 +3754,16 @@
       <c r="H111" s="1">
         <v>460</v>
       </c>
-      <c r="I111" s="1">
-        <v>0</v>
+      <c r="I111" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C112" s="1">
         <v>0</v>
@@ -3777,15 +3784,15 @@
         <v>505</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C113" s="1">
         <v>31</v>
@@ -3806,15 +3813,15 @@
         <v>480</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C114" s="1">
         <v>60</v>
@@ -3834,16 +3841,16 @@
       <c r="H114" s="1">
         <v>470</v>
       </c>
-      <c r="I114" s="1">
-        <v>0</v>
+      <c r="I114" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C115" s="1">
         <v>80</v>
@@ -3863,16 +3870,16 @@
       <c r="H115" s="1">
         <v>470</v>
       </c>
-      <c r="I115" s="1">
-        <v>0</v>
+      <c r="I115" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C116" s="1">
         <v>101</v>
@@ -3892,16 +3899,16 @@
       <c r="H116" s="1">
         <v>460</v>
       </c>
-      <c r="I116" s="1">
-        <v>0</v>
+      <c r="I116" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="1">
         <v>0</v>
@@ -3922,15 +3929,15 @@
         <v>585</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C118" s="1">
         <v>21</v>
@@ -3951,15 +3958,15 @@
         <v>545</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C119" s="1">
         <v>30</v>
@@ -3979,16 +3986,16 @@
       <c r="H119" s="1">
         <v>505</v>
       </c>
-      <c r="I119" s="1">
-        <v>0</v>
+      <c r="I119" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C120" s="1">
         <v>80</v>
@@ -4008,16 +4015,16 @@
       <c r="H120" s="1">
         <v>505</v>
       </c>
-      <c r="I120" s="1">
-        <v>0</v>
+      <c r="I120" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C121" s="1">
         <v>101</v>
@@ -4037,8 +4044,8 @@
       <c r="H121" s="1">
         <v>490</v>
       </c>
-      <c r="I121" s="1">
-        <v>0</v>
+      <c r="I121" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/ConvertData/EXCEL_MARK_STEEL/MarkSteel.xlsx
+++ b/ConvertData/EXCEL_MARK_STEEL/MarkSteel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disk\YandexDisk\001. Программирование\ForWorking\ConvertData\ConvertData\EXCEL_MARK_STEEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disk\YandexDisk\Programmings\ForWorking\ConvertData\ConvertData\EXCEL_MARK_STEEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E685E0F4-A3BE-4AE9-87DE-E0F95B9A16AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{764D00E2-6049-4EE3-A148-CEA6CE0A52A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
